--- a/Team-Data/2012-13/1-9-2012-13.xlsx
+++ b/Team-Data/2012-13/1-9-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.588</v>
+        <v>0.606</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
@@ -679,76 +746,76 @@
         <v>37.2</v>
       </c>
       <c r="J2" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K2" t="n">
         <v>0.456</v>
       </c>
       <c r="L2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>23.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="P2" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.708</v>
+        <v>0.711</v>
       </c>
       <c r="R2" t="n">
         <v>9.9</v>
       </c>
       <c r="S2" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V2" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W2" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>9</v>
@@ -757,13 +824,13 @@
         <v>12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
@@ -790,19 +857,19 @@
         <v>24</v>
       </c>
       <c r="AU2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="n">
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -814,7 +881,7 @@
         <v>13</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
         <v>48.9</v>
@@ -867,31 +934,31 @@
         <v>0.462</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="R3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>30.4</v>
       </c>
       <c r="T3" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="U3" t="n">
         <v>23.2</v>
@@ -900,7 +967,7 @@
         <v>14.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
         <v>3.9</v>
@@ -909,19 +976,19 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
         <v>19.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1</v>
+        <v>-1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -930,13 +997,13 @@
         <v>17</v>
       </c>
       <c r="AG3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="n">
         <v>16</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>15</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -951,10 +1018,10 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
@@ -972,25 +1039,25 @@
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1118,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
         <v>27</v>
@@ -1127,7 +1194,7 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM4" t="n">
         <v>8</v>
@@ -1142,7 +1209,7 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
         <v>10</v>
@@ -1157,7 +1224,7 @@
         <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
@@ -1178,7 +1245,7 @@
         <v>18</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.265</v>
+        <v>0.273</v>
       </c>
       <c r="H5" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I5" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="J5" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.425</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O5" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P5" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="R5" t="n">
         <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T5" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V5" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1270,7 +1337,7 @@
         <v>6.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
         <v>19.5</v>
@@ -1279,31 +1346,31 @@
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-7.8</v>
+        <v>-7.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
         <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH5" t="n">
         <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1312,7 +1379,7 @@
         <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN5" t="n">
         <v>19</v>
@@ -1324,25 +1391,25 @@
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU5" t="n">
         <v>29</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
         <v>29</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -1389,52 +1456,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.576</v>
+        <v>0.594</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J6" t="n">
-        <v>80.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
         <v>4.7</v>
       </c>
       <c r="M6" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="N6" t="n">
         <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.795</v>
+        <v>0.798</v>
       </c>
       <c r="R6" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
         <v>43.3</v>
@@ -1446,28 +1513,28 @@
         <v>14.9</v>
       </c>
       <c r="W6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
         <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1485,10 +1552,10 @@
         <v>24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
@@ -1512,25 +1579,25 @@
         <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
         <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ6" t="n">
         <v>12</v>
@@ -1542,7 +1609,7 @@
         <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.243</v>
+        <v>0.222</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
@@ -1589,43 +1656,43 @@
         <v>35.2</v>
       </c>
       <c r="J7" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.418</v>
+        <v>0.417</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M7" t="n">
         <v>21.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.36</v>
+        <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P7" t="n">
         <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R7" t="n">
         <v>13.1</v>
       </c>
       <c r="S7" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T7" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U7" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V7" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W7" t="n">
         <v>8.1</v>
@@ -1637,22 +1704,22 @@
         <v>7.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.3</v>
+        <v>-5.9</v>
       </c>
       <c r="AD7" t="n">
         <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
         <v>29</v>
@@ -1673,22 +1740,22 @@
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM7" t="n">
         <v>9</v>
       </c>
       <c r="AN7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
         <v>4</v>
@@ -1703,10 +1770,10 @@
         <v>30</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1715,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
@@ -1724,7 +1791,7 @@
         <v>25</v>
       </c>
       <c r="BC7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1820,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
         <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>0.361</v>
+        <v>0.371</v>
       </c>
       <c r="H8" t="n">
         <v>49.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J8" t="n">
         <v>83.59999999999999</v>
@@ -1780,28 +1847,28 @@
         <v>7.1</v>
       </c>
       <c r="M8" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
         <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T8" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U8" t="n">
         <v>21.7</v>
@@ -1810,37 +1877,37 @@
         <v>15.1</v>
       </c>
       <c r="W8" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y8" t="n">
         <v>4.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>21</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -1849,10 +1916,10 @@
         <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
         <v>14</v>
@@ -1861,7 +1928,7 @@
         <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>19</v>
@@ -1876,7 +1943,7 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1885,13 +1952,13 @@
         <v>17</v>
       </c>
       <c r="AV8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW8" t="n">
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
         <v>7</v>
@@ -1903,7 +1970,7 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,61 +2020,61 @@
         <v>39.4</v>
       </c>
       <c r="J9" t="n">
-        <v>84.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.465</v>
       </c>
       <c r="L9" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M9" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="N9" t="n">
         <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.677</v>
+        <v>0.679</v>
       </c>
       <c r="R9" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="S9" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T9" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="U9" t="n">
         <v>23.4</v>
       </c>
       <c r="V9" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X9" t="n">
         <v>6.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="AC9" t="n">
         <v>2.6</v>
@@ -2016,13 +2083,13 @@
         <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="n">
         <v>14</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
@@ -2031,22 +2098,22 @@
         <v>2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN9" t="n">
         <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2058,31 +2125,31 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2216,7 +2283,7 @@
         <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
@@ -2240,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>6</v>
@@ -2258,10 +2325,10 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
         <v>22</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.647</v>
+        <v>0.667</v>
       </c>
       <c r="H11" t="n">
         <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="J11" t="n">
-        <v>83.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K11" t="n">
         <v>0.456</v>
@@ -2326,28 +2393,28 @@
         <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O11" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="R11" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S11" t="n">
         <v>34</v>
       </c>
       <c r="T11" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U11" t="n">
         <v>22.7</v>
@@ -2359,31 +2426,31 @@
         <v>7.1</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z11" t="n">
         <v>21.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
         <v>7</v>
@@ -2392,13 +2459,13 @@
         <v>9</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2416,10 +2483,10 @@
         <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2440,13 +2507,13 @@
         <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ11" t="n">
         <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.583</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38.3</v>
+        <v>38.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L12" t="n">
         <v>9.9</v>
@@ -2511,13 +2578,13 @@
         <v>27.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O12" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="P12" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q12" t="n">
         <v>0.763</v>
@@ -2526,16 +2593,16 @@
         <v>10.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
         <v>8.800000000000001</v>
@@ -2544,40 +2611,40 @@
         <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z12" t="n">
         <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>106</v>
+        <v>106.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>8</v>
       </c>
       <c r="AF12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK12" t="n">
         <v>7</v>
@@ -2589,13 +2656,13 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>15</v>
@@ -2604,13 +2671,13 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2625,10 +2692,10 @@
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -2741,31 +2808,31 @@
         <v>1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
       </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2786,7 +2853,7 @@
         <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2807,7 +2874,7 @@
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.778</v>
+        <v>0.771</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2869,37 +2936,37 @@
         <v>0.477</v>
       </c>
       <c r="L14" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O14" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P14" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.711</v>
+        <v>0.713</v>
       </c>
       <c r="R14" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S14" t="n">
         <v>30.5</v>
       </c>
       <c r="T14" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="W14" t="n">
         <v>10.8</v>
@@ -2911,19 +2978,19 @@
         <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.8</v>
+        <v>101.9</v>
       </c>
       <c r="AC14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2965,19 +3032,19 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
         <v>17</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2992,13 +3059,13 @@
         <v>25</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB14" t="n">
         <v>8</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.429</v>
+        <v>0.441</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.454</v>
@@ -3057,55 +3124,55 @@
         <v>25.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.355</v>
+        <v>0.357</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="P15" t="n">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="S15" t="n">
         <v>32.7</v>
       </c>
       <c r="T15" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U15" t="n">
         <v>21.6</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>19</v>
@@ -3117,19 +3184,19 @@
         <v>19</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
         <v>11</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
@@ -3147,31 +3214,31 @@
         <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3180,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.697</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.439</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M16" t="n">
         <v>14.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.35</v>
+        <v>0.359</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P16" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="R16" t="n">
         <v>13.3</v>
@@ -3260,22 +3327,22 @@
         <v>43.1</v>
       </c>
       <c r="U16" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W16" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA16" t="n">
         <v>20</v>
@@ -3287,16 +3354,16 @@
         <v>5.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>3</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
@@ -3305,10 +3372,10 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,13 +3384,13 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3332,34 +3399,34 @@
         <v>3</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
         <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3502,13 +3569,13 @@
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3526,7 +3593,7 @@
         <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -3573,22 +3640,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.529</v>
+        <v>0.515</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J18" t="n">
         <v>85.8</v>
@@ -3597,13 +3664,13 @@
         <v>0.433</v>
       </c>
       <c r="L18" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.341</v>
       </c>
       <c r="O18" t="n">
         <v>16</v>
@@ -3615,25 +3682,25 @@
         <v>0.748</v>
       </c>
       <c r="R18" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S18" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T18" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U18" t="n">
         <v>21.9</v>
       </c>
       <c r="V18" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y18" t="n">
         <v>4.2</v>
@@ -3642,25 +3709,25 @@
         <v>19.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
         <v>21</v>
@@ -3675,31 +3742,31 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
       </c>
       <c r="AP18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>18</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>17</v>
-      </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>15</v>
@@ -3714,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="AY18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ18" t="n">
         <v>10</v>
@@ -3723,7 +3790,7 @@
         <v>15</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.516</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="J19" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.431</v>
       </c>
       <c r="L19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M19" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3</v>
+        <v>0.301</v>
       </c>
       <c r="O19" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P19" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="S19" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="U19" t="n">
         <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
         <v>7.7</v>
@@ -3824,13 +3891,13 @@
         <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AD19" t="n">
         <v>30</v>
@@ -3839,19 +3906,19 @@
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3860,7 +3927,7 @@
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
@@ -3869,7 +3936,7 @@
         <v>6</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
@@ -3878,16 +3945,16 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="n">
         <v>14</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>18</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.286</v>
+        <v>0.265</v>
       </c>
       <c r="H20" t="n">
         <v>48.6</v>
@@ -3955,10 +4022,10 @@
         <v>35.3</v>
       </c>
       <c r="J20" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L20" t="n">
         <v>6.9</v>
@@ -3967,82 +4034,82 @@
         <v>18.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="O20" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R20" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S20" t="n">
         <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U20" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V20" t="n">
         <v>14.3</v>
       </c>
       <c r="W20" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH20" t="n">
         <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
       </c>
       <c r="AM20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AN20" t="n">
         <v>7</v>
@@ -4060,31 +4127,31 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>5.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -4215,7 +4282,7 @@
         <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK21" t="n">
         <v>12</v>
@@ -4233,10 +4300,10 @@
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
         <v>22</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.771</v>
+        <v>0.765</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J22" t="n">
         <v>78.3</v>
@@ -4325,13 +4392,13 @@
         <v>0.478</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
         <v>19.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="O22" t="n">
         <v>22.9</v>
@@ -4346,19 +4413,19 @@
         <v>10.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U22" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
         <v>15.7</v>
       </c>
       <c r="W22" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
         <v>7.3</v>
@@ -4367,19 +4434,19 @@
         <v>3.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB22" t="n">
         <v>105.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4394,7 +4461,7 @@
         <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4403,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AN22" t="n">
         <v>1</v>
@@ -4421,13 +4488,13 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
         <v>16</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,7 +4512,7 @@
         <v>2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
         <v>9</v>
@@ -4454,7 +4521,7 @@
         <v>2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -4483,46 +4550,46 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.343</v>
+        <v>0.353</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J23" t="n">
-        <v>82.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.345</v>
       </c>
       <c r="O23" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="P23" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R23" t="n">
         <v>10.4</v>
@@ -4537,40 +4604,40 @@
         <v>22.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
         <v>5.8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y23" t="n">
         <v>4.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="AC23" t="n">
         <v>-3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
         <v>14</v>
@@ -4579,16 +4646,16 @@
         <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
       </c>
       <c r="AM23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="n">
         <v>21</v>
@@ -4609,13 +4676,13 @@
         <v>7</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4624,16 +4691,16 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -4665,37 +4732,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>0.405</v>
+        <v>0.417</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J24" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L24" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M24" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="O24" t="n">
         <v>12.6</v>
@@ -4704,43 +4771,43 @@
         <v>17.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.722</v>
       </c>
       <c r="R24" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S24" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="V24" t="n">
         <v>12.8</v>
       </c>
       <c r="W24" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X24" t="n">
         <v>5.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="n">
         <v>17</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.5</v>
+        <v>-4.1</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
@@ -4758,22 +4825,22 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM24" t="n">
         <v>22</v>
       </c>
-      <c r="AL24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>23</v>
-      </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,28 +4855,28 @@
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
         <v>16</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4818,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>0.324</v>
+        <v>0.333</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J25" t="n">
         <v>84.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M25" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.326</v>
+        <v>0.329</v>
       </c>
       <c r="O25" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="P25" t="n">
         <v>19.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.748</v>
+        <v>0.751</v>
       </c>
       <c r="R25" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="S25" t="n">
         <v>28.9</v>
       </c>
       <c r="T25" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="U25" t="n">
         <v>22</v>
       </c>
       <c r="V25" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W25" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X25" t="n">
         <v>5.7</v>
@@ -4913,22 +4980,22 @@
         <v>5.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="AD25" t="n">
         <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
         <v>26</v>
@@ -4943,16 +5010,16 @@
         <v>7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="n">
         <v>28</v>
@@ -4964,10 +5031,10 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR25" t="n">
         <v>18</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>16</v>
       </c>
       <c r="AS25" t="n">
         <v>28</v>
@@ -4982,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -4991,16 +5058,16 @@
         <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BC25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -5107,28 +5174,28 @@
         <v>-1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>13</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
         <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
@@ -5152,7 +5219,7 @@
         <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
         <v>22</v>
@@ -5170,7 +5237,7 @@
         <v>21</v>
       </c>
       <c r="AY26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>21</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>21</v>
@@ -5304,7 +5371,7 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
         <v>11</v>
@@ -5316,19 +5383,19 @@
         <v>16</v>
       </c>
       <c r="AM27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP27" t="n">
         <v>15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
@@ -5343,28 +5410,28 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY27" t="n">
         <v>26</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>0.737</v>
+        <v>0.73</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="J28" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K28" t="n">
         <v>0.484</v>
       </c>
       <c r="L28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="O28" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.795</v>
+        <v>0.793</v>
       </c>
       <c r="R28" t="n">
         <v>8.5</v>
       </c>
       <c r="S28" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="T28" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U28" t="n">
         <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W28" t="n">
         <v>8.699999999999999</v>
@@ -5456,19 +5523,19 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
         <v>104.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5498,7 +5565,7 @@
         <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN28" t="n">
         <v>4</v>
@@ -5507,16 +5574,16 @@
         <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
         <v>19</v>
@@ -5525,16 +5592,16 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
         <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
         <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>0.371</v>
+        <v>0.353</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J29" t="n">
         <v>81.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="M29" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.34</v>
+        <v>0.344</v>
       </c>
       <c r="O29" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P29" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R29" t="n">
         <v>10.3</v>
       </c>
       <c r="S29" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T29" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U29" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V29" t="n">
         <v>12.7</v>
@@ -5635,40 +5702,40 @@
         <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
         <v>5.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.5</v>
+        <v>96.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF29" t="n">
         <v>21</v>
       </c>
-      <c r="AF29" t="n">
-        <v>20</v>
-      </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
         <v>19</v>
@@ -5677,16 +5744,16 @@
         <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
         <v>13</v>
@@ -5698,7 +5765,7 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5710,19 +5777,19 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BB29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -5757,58 +5824,58 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J30" t="n">
         <v>82.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.444</v>
+        <v>0.441</v>
       </c>
       <c r="L30" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M30" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.368</v>
+        <v>0.365</v>
       </c>
       <c r="O30" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P30" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R30" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T30" t="n">
         <v>42.9</v>
       </c>
       <c r="U30" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
@@ -5817,7 +5884,7 @@
         <v>8.1</v>
       </c>
       <c r="X30" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
         <v>6.2</v>
@@ -5829,16 +5896,16 @@
         <v>20.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5850,19 +5917,19 @@
         <v>18</v>
       </c>
       <c r="AI30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ30" t="n">
         <v>17</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN30" t="n">
         <v>9</v>
@@ -5871,10 +5938,10 @@
         <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>6</v>
@@ -5883,7 +5950,7 @@
         <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
         <v>10</v>
@@ -5892,7 +5959,7 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5907,10 +5974,10 @@
         <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6035,7 +6102,7 @@
         <v>29</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6056,13 +6123,13 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT31" t="n">
         <v>7</v>
@@ -6077,7 +6144,7 @@
         <v>24</v>
       </c>
       <c r="AX31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-9-2012-13</t>
+          <t>2013-01-09</t>
         </is>
       </c>
     </row>
